--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\ServerTest\ConsoleApp1\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3880BB63-B642-4EA9-AB9E-CAEC92F38A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B2A789-6FAD-40A1-B19B-B701F9E17A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,18 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>canEat</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canUse</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>canDrop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -63,14 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>宝剑</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色的武器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>小红药</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -99,15 +79,135 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否可以吃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否可以用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否可以丢弃</t>
+    <t>ItemType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对hp的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对mp的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对攻击力的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Def</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御力的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对其他属性的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加20点攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初级盔甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加20点防御力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移速鞋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加2点移速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpritePath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初级宝剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Addition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CanbeDrop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以被丢弃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>def1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>addition1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atk1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResouresPath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源路径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Def1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -151,10 +251,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,10 +539,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="19.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,114 +553,451 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="L2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1" t="b">
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="b">
         <v>1</v>
       </c>
-      <c r="F4" s="1" t="b">
+      <c r="L6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="b">
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>20</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>1003</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="L7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B2A789-6FAD-40A1-B19B-B701F9E17A77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F07244-ABFE-4960-9F6C-1EA34566DF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,26 +167,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hp1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hp2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>def1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>addition1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>atk1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ResouresPath</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -208,6 +188,58 @@
   </si>
   <si>
     <t>Def1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConsumableType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗品类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/atk1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/hp1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/hp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/def1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/addition1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxMp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对最大生命值的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对最大蓝量的增加值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,10 +571,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="19.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,32 +587,44 @@
       <c r="D1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="P1" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -593,10 +637,10 @@
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -609,16 +653,28 @@
         <v>3</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -631,32 +687,44 @@
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="P3" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -667,34 +735,46 @@
         <v>24</v>
       </c>
       <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>20</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="P4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -705,34 +785,46 @@
         <v>7</v>
       </c>
       <c r="D5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
         <v>10</v>
       </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" t="b">
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="P5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -743,34 +835,46 @@
         <v>9</v>
       </c>
       <c r="D6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
         <v>20</v>
       </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
       <c r="H6" s="2">
         <v>0</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="b">
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" t="b">
         <v>1</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="P6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -781,34 +885,46 @@
         <v>26</v>
       </c>
       <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
       <c r="F7" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
         <v>20</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" t="b">
+      <c r="M7" s="2">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -819,13 +935,13 @@
         <v>28</v>
       </c>
       <c r="D8" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -834,16 +950,28 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
         <v>2</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="N8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -852,8 +980,12 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -862,8 +994,12 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -872,8 +1008,12 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -882,8 +1022,12 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -892,8 +1036,12 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -902,8 +1050,12 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -912,8 +1064,12 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -922,8 +1078,12 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -932,8 +1092,12 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -942,8 +1106,12 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -952,8 +1120,12 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -962,8 +1134,12 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -972,8 +1148,12 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -982,8 +1162,12 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -992,12 +1176,18 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F07244-ABFE-4960-9F6C-1EA34566DF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B1F8ED-837F-4133-85B4-9DABA442413B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,18 +123,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>增加20点攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>初级盔甲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>增加20点防御力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>移速鞋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -240,6 +232,34 @@
   </si>
   <si>
     <t>对最大蓝量的增加值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级宝剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加20点攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加40点攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加20点防御力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/atk2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Atk2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -588,10 +608,10 @@
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>15</v>
@@ -600,10 +620,10 @@
         <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>19</v>
@@ -612,16 +632,16 @@
         <v>21</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -688,10 +708,10 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
@@ -700,10 +720,10 @@
         <v>18</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>20</v>
@@ -715,13 +735,13 @@
         <v>23</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -729,10 +749,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -765,13 +785,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -815,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -865,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -879,10 +899,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -915,13 +935,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -929,10 +949,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -965,25 +985,61 @@
         <v>2</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>40</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
@@ -998,6 +1054,9 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
+      <c r="P10" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36B1F8ED-837F-4133-85B4-9DABA442413B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B8C35B-BDA8-4F34-AA61-01418D77EE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -259,7 +259,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>鸡肉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后增加50点最大生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/maxHp1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> MaxHp1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -593,6 +605,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="19.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="25.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -1042,20 +1057,53 @@
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>50</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
       <c r="P10" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B8C35B-BDA8-4F34-AA61-01418D77EE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B280C2-3BF9-4A38-ABB4-4030922E04E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,30 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ResouresPath</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资源路径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Atk1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hp1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hp2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Def1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>EquipType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -255,10 +231,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Atk2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>鸡肉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -271,7 +243,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> MaxHp1</t>
+    <t>UnitId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应实体id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,10 +599,10 @@
         <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>15</v>
@@ -635,10 +611,10 @@
         <v>17</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>19</v>
@@ -656,7 +632,7 @@
         <v>31</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
@@ -706,7 +682,7 @@
         <v>5</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -723,10 +699,10 @@
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>16</v>
@@ -735,10 +711,10 @@
         <v>18</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>20</v>
@@ -756,7 +732,7 @@
         <v>32</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -767,7 +743,7 @@
         <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -800,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>35</v>
+      <c r="P4" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
@@ -850,13 +826,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>36</v>
+      <c r="P5" s="2">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -900,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>37</v>
+      <c r="P6" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -917,7 +893,7 @@
         <v>24</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -950,13 +926,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>38</v>
+      <c r="P7" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
@@ -1000,9 +976,12 @@
         <v>2</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1011,10 +990,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -1047,13 +1026,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>57</v>
+      <c r="P9" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -1061,10 +1040,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2">
         <v>0</v>
@@ -1097,13 +1076,13 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>61</v>
+      <c r="P10" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B280C2-3BF9-4A38-ABB4-4030922E04E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218036A-BF27-46AC-8A75-A0DC7453FC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -248,6 +248,14 @@
   </si>
   <si>
     <t>对应实体id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Price</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>售价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -579,13 +587,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="19.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,8 +642,11 @@
       <c r="P1" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q1" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -684,8 +695,11 @@
       <c r="P2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -734,8 +748,11 @@
       <c r="P3" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q3" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -784,8 +801,11 @@
       <c r="P4" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q4" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -834,8 +854,11 @@
       <c r="P5" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q5" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -884,8 +907,11 @@
       <c r="P6" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q6" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
@@ -934,8 +960,11 @@
       <c r="P7" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
@@ -984,8 +1013,11 @@
       <c r="P8" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
@@ -1034,8 +1066,11 @@
       <c r="P9" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
@@ -1084,8 +1119,11 @@
       <c r="P10" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1099,7 +1137,7 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1113,7 +1151,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1127,7 +1165,7 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1141,7 +1179,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1155,7 +1193,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218036A-BF27-46AC-8A75-A0DC7453FC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFD790E-8669-4EE0-A0F9-A66981DC2E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="96">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,18 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回复10点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>牛肉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复20点生命值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>物品id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -215,14 +203,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>装备后增加20点攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>装备后增加40点攻击力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>装备后增加20点防御力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -256,6 +236,176 @@
   </si>
   <si>
     <t>售价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemQuality</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>物品价值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大红药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后回复50点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后回复20点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后回复30点生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/hp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后增加100点最大生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/maxHp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四叶草</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后增加200点最大生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/maxHp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小蓝药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后回复20点蓝量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后回复30点蓝量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/mp1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/mp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/mp3</t>
+  </si>
+  <si>
+    <t>使用后回复50点蓝量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大蓝药</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>披萨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后增加30点最大蓝量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/maxMp1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔法扇贝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后增加50点最大蓝量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/maxMp3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/maxMp2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用后增加70点最大蓝量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高级宝剑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加30点攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加50点攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加100点攻击力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/atk3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中级盔甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加50点防御力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/def2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/Item/def3</t>
+  </si>
+  <si>
+    <t>高级盔甲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装备后增加100点防御力</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -587,13 +737,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="19.25" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="25.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,49 +754,52 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -698,69 +851,75 @@
       <c r="Q2" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="N3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -784,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -793,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -804,8 +963,11 @@
       <c r="Q4" s="2">
         <v>500</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -813,7 +975,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -825,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -846,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -857,16 +1019,19 @@
       <c r="Q5" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -878,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
@@ -899,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -910,16 +1075,19 @@
       <c r="Q6" s="2">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
@@ -952,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -963,16 +1131,19 @@
       <c r="Q7" s="2">
         <v>300</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
@@ -1005,7 +1176,7 @@
         <v>2</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="O8" t="b">
         <v>0</v>
@@ -1016,16 +1187,19 @@
       <c r="Q8" s="2">
         <v>400</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2">
         <v>0</v>
@@ -1049,7 +1223,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="2">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1058,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -1069,19 +1243,22 @@
       <c r="Q9" s="2">
         <v>800</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="2">
         <v>-1</v>
@@ -1111,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -1122,176 +1299,683 @@
       <c r="Q10" s="2">
         <v>400</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>50</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>500</v>
+      </c>
+      <c r="R11" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>100</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>600</v>
+      </c>
+      <c r="R12" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>200</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>800</v>
+      </c>
+      <c r="R13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>20</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>200</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>400</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>50</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>600</v>
+      </c>
+      <c r="R16" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>30</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O17" t="b">
+        <v>1</v>
+      </c>
+      <c r="P17" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>300</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>50</v>
+      </c>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>500</v>
+      </c>
+      <c r="R18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D19" s="2">
+        <v>1</v>
+      </c>
+      <c r="E19" s="2">
+        <v>-1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>70</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>700</v>
+      </c>
+      <c r="R19" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2">
+        <v>100</v>
+      </c>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="R20" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2">
+        <v>50</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>500</v>
+      </c>
+      <c r="R21" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>100</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>900</v>
+      </c>
+      <c r="R22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1305,7 +1989,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>

--- a/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
+++ b/MMORPG_SERVER/Data/Excel/ItemDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\game\MMORPG_GAME_SERVER\MMORPG_SERVER\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AFD790E-8669-4EE0-A0F9-A66981DC2E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B934AEC2-98A8-41B9-9948-BCC08CA0E7E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1656,7 +1656,7 @@
         <v>-1</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="2">
         <v>0</v>
@@ -1712,7 +1712,7 @@
         <v>-1</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2">
         <v>0</v>
@@ -1768,7 +1768,7 @@
         <v>-1</v>
       </c>
       <c r="F19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="2">
         <v>0</v>
